--- a/document/開発タスク_20250425.xlsx
+++ b/document/開発タスク_20250425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F245C8CA-C199-48A2-9E63-E89951F9A3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7279E89E-F7AC-4CD0-8F6D-E647E8F93782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="204">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2752,12 +2752,37 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>項目追加</t>
+    <t>項目追加 : 問題情報ID,カテゴリーID,問題タイトル、問題内容</t>
     <rPh sb="0" eb="2">
       <t>コウモク</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ツイカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報登録 : edu_issue</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4075,9 +4100,11 @@
         <v>45772</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E21" s="12">
+        <v>45772</v>
+      </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
         <v>14</v>
@@ -4101,10 +4128,13 @@
         <v>45772</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="13">
+        <f>$B$21</f>
+        <v>19</v>
+      </c>
       <c r="G22" s="13" t="s">
         <v>14</v>
       </c>
@@ -4115,7 +4145,7 @@
         <v>201</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
@@ -4123,14 +4153,29 @@
         <f t="shared" ref="B23" si="3">B22+1</f>
         <v>21</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="12">
+        <v>45772</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15"/>
+      <c r="F23" s="13">
+        <f>$B$21</f>
+        <v>19</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
@@ -7378,7 +7423,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H140:H142 H93:H104 H3:H68 H91</xm:sqref>
+          <xm:sqref>H140:H142 H93:H104 H91 H3:H68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>

--- a/document/開発タスク_20250425.xlsx
+++ b/document/開発タスク_20250425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7279E89E-F7AC-4CD0-8F6D-E647E8F93782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753A322-357F-4CB4-8A18-F74BF6930E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="205">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2783,6 +2783,19 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期登録 : saveメソッド追加</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4157,9 +4170,11 @@
         <v>45772</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E23" s="12">
+        <v>45772</v>
+      </c>
       <c r="F23" s="13">
         <f>$B$21</f>
         <v>19</v>
@@ -4182,14 +4197,29 @@
         <f t="shared" ref="B24" si="4">B23+1</f>
         <v>22</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
+      <c r="C24" s="12">
+        <v>45772</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
+      <c r="F24" s="13">
+        <f>$B$21</f>
+        <v>19</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
